--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/valparaiso.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M243"/>
+  <dimension ref="A1:M244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3202,7 +3202,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3134-3-CM26</t>
+          <t>1431841-2-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2036.73</v>
+        <v>5648.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1431841-2-CM26</t>
+          <t>3134-3-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5648.88</v>
+        <v>2036.73</v>
       </c>
     </row>
     <row r="48">
@@ -4178,7 +4178,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>799512-29-CM26</t>
+          <t>4469-63-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4198,17 +4198,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5011.09</v>
+        <v>1965.86</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4469-63-CM26</t>
+          <t>799512-29-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1965.86</v>
+        <v>5011.09</v>
       </c>
     </row>
     <row r="64">
@@ -5093,7 +5093,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4964-16-CM26</t>
+          <t>3232-86-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2829.34</v>
+        <v>597.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3232-86-CM26</t>
+          <t>4964-16-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>597.12</v>
+        <v>2829.34</v>
       </c>
     </row>
     <row r="79">
@@ -5825,7 +5825,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4469-84-CM26</t>
+          <t>4469-82-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3364.13</v>
+        <v>1867.63</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4469-83-CM26</t>
+          <t>4469-84-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>791</v>
+        <v>3364.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4469-82-CM26</t>
+          <t>4469-83-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1867.63</v>
+        <v>791</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5514-13-CM26</t>
+          <t>3129-25-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6028,17 +6028,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>61.970.200-K</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>DIRECCION DE INTELIGENCIA DE LA ARMADA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>66625.48</v>
+        <v>10195.92</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3232-151-CM26</t>
+          <t>5514-13-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6089,17 +6089,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>20207.39</v>
+        <v>66625.48</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3129-25-CM26</t>
+          <t>3232-151-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.970.200-K</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIRECCION DE INTELIGENCIA DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>10195.92</v>
+        <v>20207.39</v>
       </c>
     </row>
     <row r="95">
@@ -6862,7 +6862,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3621-94-CM26</t>
+          <t>2687-47-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5683.48</v>
+        <v>10103.7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3560-54-CM26</t>
+          <t>1035206-52-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>23886.87</v>
+        <v>23924.95</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1035206-52-CM26</t>
+          <t>3621-94-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7004,17 +7004,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>23924.95</v>
+        <v>5683.48</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2687-47-CM26</t>
+          <t>3560-54-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7065,17 +7065,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10103.7</v>
+        <v>23886.87</v>
       </c>
     </row>
     <row r="110">
@@ -7350,7 +7350,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1134432-202-CM26</t>
+          <t>799512-259-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7370,17 +7370,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1910.99</v>
+        <v>3819.9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2833-286-CM26</t>
+          <t>1134432-202-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7431,17 +7431,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.930.600-7</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>9398.620000000001</v>
+        <v>1910.99</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>799512-259-CM26</t>
+          <t>2833-286-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>61.930.600-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3819.9</v>
+        <v>9398.620000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7899,7 +7899,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4283-76-CM26</t>
+          <t>2694-43-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.050.900-8</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CATEMU</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>7119.04</v>
+        <v>621.75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2694-42-CM26</t>
+          <t>4283-76-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.050.900-8</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE CATEMU</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>22919.4</v>
+        <v>7119.04</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2694-43-CM26</t>
+          <t>2694-42-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>621.75</v>
+        <v>22919.4</v>
       </c>
     </row>
     <row r="126">
@@ -8631,7 +8631,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3882-135-CM26</t>
+          <t>1368250-2-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>65.202.964-7</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>ASOCIACION DE MUNICIPALIDADES DE LA CUENCA DEL LAGO LLANQUIHUE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3974.84</v>
+        <v>2388.33</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1368250-2-CM26</t>
+          <t>3882-135-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>65.202.964-7</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES DE LA CUENCA DEL LAGO LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2388.33</v>
+        <v>3974.84</v>
       </c>
     </row>
     <row r="137">
@@ -8936,7 +8936,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1048-154-CM26</t>
+          <t>1439295-5-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8956,17 +8956,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>65.190.295-9</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>ASOCIACION DE MUNICIPALIDADES TURISTICAS DE CHILE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>35214.36</v>
+        <v>963.89</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1439295-5-CM26</t>
+          <t>1048-154-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9017,17 +9017,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>65.190.295-9</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES TURISTICAS DE CHILE</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>963.89</v>
+        <v>35214.36</v>
       </c>
     </row>
     <row r="142">
@@ -9741,7 +9741,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5300-17-CM26</t>
+          <t>2687-80-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9796,13 +9796,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>783.97</v>
+        <v>4071.7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2687-80-CM26</t>
+          <t>5300-17-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9842,12 +9842,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9857,13 +9857,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4071.7</v>
+        <v>783.97</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>799512-407-CM26</t>
+          <t>1048-178-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9883,17 +9883,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9918,13 +9918,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1237.6</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1048-177-CM26</t>
+          <t>799512-407-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9944,17 +9944,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9979,13 +9979,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6110.13</v>
+        <v>1237.6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1048-178-CM26</t>
+          <t>1048-177-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2593</v>
+        <v>6110.13</v>
       </c>
     </row>
     <row r="158">
@@ -11266,7 +11266,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>568658-840-CM26</t>
+          <t>3244-221-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11291,12 +11291,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11321,13 +11321,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>12743.83</v>
+        <v>6687.21</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3244-221-CM26</t>
+          <t>568658-840-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11382,7 +11382,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>6687.21</v>
+        <v>12743.83</v>
       </c>
     </row>
     <row r="180">
@@ -11571,7 +11571,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4964-46-CM26</t>
+          <t>4469-432-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11611,12 +11611,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11626,13 +11626,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1044.8</v>
+        <v>5074.16</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4469-432-CM26</t>
+          <t>4301-384-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11657,12 +11657,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>5074.16</v>
+        <v>442.68</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4469-433-CM26</t>
+          <t>4469-434-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11748,13 +11748,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5550.56</v>
+        <v>762.17</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4469-434-CM26</t>
+          <t>4964-46-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11774,17 +11774,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11794,12 +11794,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11809,13 +11809,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>762.17</v>
+        <v>1044.8</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4301-384-CM26</t>
+          <t>4469-433-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11870,7 +11870,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>442.68</v>
+        <v>5550.56</v>
       </c>
     </row>
     <row r="188">
@@ -12242,7 +12242,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>629373-156-CM26</t>
+          <t>629373-154-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12282,12 +12282,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12297,13 +12297,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1627.21</v>
+        <v>8473.32</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2688-189-CM26</t>
+          <t>629373-155-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12323,17 +12323,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>70.962.500-4</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12343,12 +12343,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12358,13 +12358,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2521.57</v>
+        <v>48666.24</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>629373-154-CM26</t>
+          <t>629373-156-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12419,13 +12419,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>8473.32</v>
+        <v>1627.21</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>629373-155-CM26</t>
+          <t>2688-189-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12445,17 +12445,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>70.962.500-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12480,13 +12480,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>48666.24</v>
+        <v>2521.57</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5251-496-CM26</t>
+          <t>799512-676-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12506,17 +12506,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>13939.07</v>
+        <v>8350.110000000001</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5251-498-CM26</t>
+          <t>899-413-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12567,17 +12567,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>61.602.067-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>Hospital San Jose - Casablanca</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1612.27</v>
+        <v>24553.03</v>
       </c>
     </row>
     <row r="200">
@@ -12669,7 +12669,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>899-413-CM26</t>
+          <t>5251-498-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12689,17 +12689,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.602.067-6</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12724,13 +12724,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>24553.03</v>
+        <v>1612.27</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>799512-676-CM26</t>
+          <t>5251-496-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12750,17 +12750,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12770,12 +12770,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>8350.110000000001</v>
+        <v>13939.07</v>
       </c>
     </row>
     <row r="203">
@@ -13035,7 +13035,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>640840-100-CM26</t>
+          <t>4895-136-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13090,13 +13090,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>666.4</v>
+        <v>47530.62</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4895-136-CM26</t>
+          <t>836-114-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13151,13 +13151,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>47530.62</v>
+        <v>5084.16</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>836-114-CM26</t>
+          <t>836-115-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13197,12 +13197,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>5084.16</v>
+        <v>6172.53</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>836-115-CM26</t>
+          <t>640840-100-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>6172.53</v>
+        <v>666.4</v>
       </c>
     </row>
     <row r="211">
@@ -13340,7 +13340,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4044-463-CM26</t>
+          <t>2696-72-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.061.800-1</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13380,12 +13380,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13395,13 +13395,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>74596.97</v>
+        <v>986.64</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2696-72-CM26</t>
+          <t>4044-463-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13421,17 +13421,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13456,13 +13456,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>986.64</v>
+        <v>74596.97</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>701-304-CM26</t>
+          <t>2428-732-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13482,17 +13482,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13502,32 +13502,28 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.819.088-7</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>241950.8</v>
+        <v>1527.96</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>799512-711-CM26</t>
+          <t>701-304-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13547,17 +13543,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13567,28 +13563,32 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>8306.1</v>
+        <v>241950.8</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2428-732-CM26</t>
+          <t>799512-711-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13613,12 +13613,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13643,7 +13643,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1527.96</v>
+        <v>8306.1</v>
       </c>
     </row>
     <row r="217">
@@ -14137,7 +14137,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5251-539-CM26</t>
+          <t>799512-732-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14192,13 +14192,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4757.03</v>
+        <v>4942.77</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>799512-732-CM26</t>
+          <t>5251-539-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14218,17 +14218,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14238,12 +14238,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14253,13 +14253,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>4942.77</v>
+        <v>4757.03</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2920-149-CM26</t>
+          <t>2687-121-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14284,12 +14284,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14299,12 +14299,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14314,13 +14314,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1021.94</v>
+        <v>3996.32</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2687-121-CM26</t>
+          <t>2628-183-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14375,13 +14375,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3996.32</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2628-183-CM26</t>
+          <t>2920-149-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14406,12 +14406,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14421,12 +14421,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>4641</v>
+        <v>1021.94</v>
       </c>
     </row>
     <row r="230">
@@ -14808,7 +14808,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>836-125-CM26</t>
+          <t>1480972-376-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>SLEP MARGA MARGA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14863,13 +14863,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>5669.99</v>
+        <v>25074.55</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1480972-376-CM26</t>
+          <t>4469-686-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -14924,13 +14924,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>25074.55</v>
+        <v>3388.31</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4469-686-CM26</t>
+          <t>836-125-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14955,12 +14955,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14970,12 +14970,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3388.31</v>
+        <v>5669.99</v>
       </c>
     </row>
     <row r="239">
@@ -15174,7 +15174,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2428-793-CM26</t>
+          <t>640840-125-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15199,12 +15199,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15229,13 +15229,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1055.16</v>
+        <v>1281.42</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>640840-125-CM26</t>
+          <t>2428-793-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15260,12 +15260,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15275,12 +15275,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15290,7 +15290,68 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1281.42</v>
+        <v>1055.16</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>5839-38-CM26</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>61.102.016-3</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="n">
+        <v>30421.76</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/valparaiso.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M512"/>
+  <dimension ref="A1:M511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16886,7 +16886,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4469-63-CM26</t>
+          <t>799512-29-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16906,17 +16906,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16926,32 +16926,28 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1965.86</v>
+        <v>5011.09</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>799512-29-CM26</t>
+          <t>4469-63-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16971,17 +16967,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16991,22 +16987,26 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
+          <t>78.218.816-K</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>5011.09</v>
+        <v>1965.86</v>
       </c>
     </row>
     <row r="260">
@@ -17463,7 +17463,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2696-11-CM26</t>
+          <t>3073-33-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17483,17 +17483,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17503,12 +17503,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17522,13 +17522,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>829</v>
+        <v>3096.38</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3073-33-CM26</t>
+          <t>2696-11-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17548,17 +17548,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17568,12 +17568,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>3096.38</v>
+        <v>829</v>
       </c>
     </row>
     <row r="269">
@@ -17979,7 +17979,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3693-15-CM26</t>
+          <t>3693-13-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18019,12 +18019,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -18038,13 +18038,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>29516.9</v>
+        <v>5537.03</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3693-13-CM26</t>
+          <t>3693-15-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5537.03</v>
+        <v>29516.9</v>
       </c>
     </row>
     <row r="277">
@@ -18694,7 +18694,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>4469-84-CM26</t>
+          <t>4469-83-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18734,12 +18734,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -18753,13 +18753,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>3364.13</v>
+        <v>791</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>4469-83-CM26</t>
+          <t>4469-84-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18799,12 +18799,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -18818,7 +18818,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>791</v>
+        <v>3364.13</v>
       </c>
     </row>
     <row r="288">
@@ -19271,7 +19271,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4686-193-CM26</t>
+          <t>3047-86-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19291,17 +19291,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19311,22 +19311,26 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>16040.96</v>
+        <v>3061.63</v>
       </c>
     </row>
     <row r="296">
@@ -19393,7 +19397,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3047-86-CM26</t>
+          <t>4686-193-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19413,17 +19417,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19433,26 +19437,22 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3061.63</v>
+        <v>16040.96</v>
       </c>
     </row>
     <row r="298">
@@ -19523,7 +19523,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2950-122-CM26</t>
+          <t>4469-118-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19543,17 +19543,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.102.010-4</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19563,28 +19563,32 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>5246.83</v>
+        <v>541.45</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4469-118-CM26</t>
+          <t>2950-122-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19604,17 +19608,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.102.010-4</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19624,32 +19628,28 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>541.45</v>
+        <v>5246.83</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2687-47-CM26</t>
+          <t>1035206-52-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19669,17 +19669,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19689,17 +19689,17 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -19708,13 +19708,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>10103.7</v>
+        <v>23924.95</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1035206-52-CM26</t>
+          <t>3621-94-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19734,17 +19734,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19754,12 +19754,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -19773,7 +19773,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>23924.95</v>
+        <v>5683.48</v>
       </c>
     </row>
     <row r="303">
@@ -19840,7 +19840,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>3621-94-CM26</t>
+          <t>2687-47-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19865,12 +19865,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19880,17 +19880,17 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>5683.48</v>
+        <v>10103.7</v>
       </c>
     </row>
     <row r="305">
@@ -20478,7 +20478,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3882-116-CM26</t>
+          <t>2026-301-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20503,12 +20503,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20518,28 +20518,32 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>27651.58</v>
+        <v>15540.48</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2424-370-CM26</t>
+          <t>3882-116-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20564,12 +20568,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20579,32 +20583,28 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2315.47</v>
+        <v>27651.58</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-301-CM26</t>
+          <t>2211-327-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20629,12 +20629,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20644,32 +20644,28 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>15540.48</v>
+        <v>9472.4</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2211-327-CM26</t>
+          <t>2424-370-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20694,12 +20690,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20709,22 +20705,26 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K317" t="inlineStr"/>
+          <t>77.137.827-7</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>9472.4</v>
+        <v>2315.47</v>
       </c>
     </row>
     <row r="318">
@@ -21177,7 +21177,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1725-213-CM26</t>
+          <t>2833-330-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21202,12 +21202,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.930.600-7</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21217,12 +21217,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -21236,13 +21236,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>21267.68</v>
+        <v>11277.63</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2833-330-CM26</t>
+          <t>1725-213-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21267,12 +21267,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.930.600-7</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21282,12 +21282,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -21301,7 +21301,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>11277.63</v>
+        <v>21267.68</v>
       </c>
     </row>
     <row r="327">
@@ -21368,7 +21368,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5514-29-CM26</t>
+          <t>3778-114-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21388,17 +21388,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21408,12 +21408,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -21427,13 +21427,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>36336.17</v>
+        <v>146.73</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>3778-114-CM26</t>
+          <t>5514-29-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21453,17 +21453,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21473,12 +21473,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>146.73</v>
+        <v>36336.17</v>
       </c>
     </row>
     <row r="330">
@@ -21624,7 +21624,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1456835-4-CM26</t>
+          <t>1456835-3-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21664,32 +21664,28 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>6083.88</v>
+        <v>7640.75</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1456835-3-CM26</t>
+          <t>1456835-4-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21729,22 +21725,26 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>7640.75</v>
+        <v>6083.88</v>
       </c>
     </row>
     <row r="334">
@@ -21937,7 +21937,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>4301-259-CM26</t>
+          <t>3110-105-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21962,12 +21962,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.102.033-3</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21977,12 +21977,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -21996,13 +21996,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>814.34</v>
+        <v>791</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>3110-105-CM26</t>
+          <t>4301-259-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22027,12 +22027,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.102.033-3</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22042,12 +22042,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -22061,7 +22061,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>791</v>
+        <v>814.34</v>
       </c>
     </row>
     <row r="339">
@@ -22262,7 +22262,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>3084-62-SE26</t>
+          <t>3084-60-SE26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22302,12 +22302,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -22321,13 +22321,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>47293.08</v>
+        <v>46741.68</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>3084-60-SE26</t>
+          <t>3084-62-SE26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22367,12 +22367,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -22386,7 +22386,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>46741.68</v>
+        <v>47293.08</v>
       </c>
     </row>
     <row r="344">
@@ -22648,7 +22648,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5300-17-CM26</t>
+          <t>2687-80-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22673,12 +22673,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22688,12 +22688,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -22707,13 +22707,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>783.97</v>
+        <v>4071.7</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2687-80-CM26</t>
+          <t>5300-17-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22738,12 +22738,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22753,12 +22753,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -22772,13 +22772,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>4071.7</v>
+        <v>783.97</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>799512-407-CM26</t>
+          <t>1048-177-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22798,17 +22798,17 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22818,28 +22818,32 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr"/>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>1237.6</v>
+        <v>6110.13</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1048-177-CM26</t>
+          <t>1048-178-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22879,12 +22883,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -22898,13 +22902,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>6110.13</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1048-178-CM26</t>
+          <t>799512-407-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -22924,17 +22928,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22944,32 +22948,28 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2593</v>
+        <v>1237.6</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>4469-301-CM26</t>
+          <t>4469-300-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>416.5</v>
+        <v>3627.05</v>
       </c>
     </row>
     <row r="354">
@@ -23160,7 +23160,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>4469-300-CM26</t>
+          <t>4469-301-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23200,12 +23200,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -23219,7 +23219,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3627.05</v>
+        <v>416.5</v>
       </c>
     </row>
     <row r="357">
@@ -23802,7 +23802,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1132470-34-CM26</t>
+          <t>3073-219-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23827,12 +23827,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>62.000.820-6</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -23842,12 +23842,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K366" t="inlineStr"/>
@@ -23857,13 +23857,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>13610.84</v>
+        <v>257.04</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>3073-219-CM26</t>
+          <t>1132470-34-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23888,12 +23888,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>62.000.820-6</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -23903,12 +23903,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K367" t="inlineStr"/>
@@ -23918,7 +23918,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>257.04</v>
+        <v>13610.84</v>
       </c>
     </row>
     <row r="368">
@@ -23985,7 +23985,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2626-244-CM26</t>
+          <t>799512-535-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24010,12 +24010,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24025,28 +24025,32 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>6781.73</v>
+        <v>6178.47</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>799512-535-CM26</t>
+          <t>2626-244-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24071,12 +24075,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24086,26 +24090,22 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>6178.47</v>
+        <v>6781.73</v>
       </c>
     </row>
     <row r="371">
@@ -24241,7 +24241,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>568658-840-CM26</t>
+          <t>3244-221-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24266,12 +24266,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24281,12 +24281,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -24300,13 +24300,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>12743.83</v>
+        <v>6687.21</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3244-221-CM26</t>
+          <t>568658-840-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24331,12 +24331,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24346,12 +24346,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -24365,7 +24365,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>6687.21</v>
+        <v>12743.83</v>
       </c>
     </row>
     <row r="375">
@@ -24566,7 +24566,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>4964-46-CM26</t>
+          <t>4301-384-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24586,17 +24586,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -24606,32 +24606,28 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1044.8</v>
+        <v>442.68</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>4469-432-CM26</t>
+          <t>4469-434-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24671,32 +24667,28 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K379" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>5074.16</v>
+        <v>762.17</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>4469-433-CM26</t>
+          <t>4964-46-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -24716,17 +24708,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -24736,28 +24728,32 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K380" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>5550.56</v>
+        <v>1044.8</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>4469-434-CM26</t>
+          <t>4469-432-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24797,28 +24793,32 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K381" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>762.17</v>
+        <v>5074.16</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4301-384-CM26</t>
+          <t>4469-433-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -24843,12 +24843,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
@@ -24873,7 +24873,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>442.68</v>
+        <v>5550.56</v>
       </c>
     </row>
     <row r="383">
@@ -25196,7 +25196,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2688-189-CM26</t>
+          <t>629373-155-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25216,17 +25216,17 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>70.962.500-4</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25236,12 +25236,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -25255,7 +25255,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>2521.57</v>
+        <v>48666.24</v>
       </c>
     </row>
     <row r="389">
@@ -25326,7 +25326,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>629373-155-CM26</t>
+          <t>2688-189-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25346,17 +25346,17 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>70.962.500-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25366,12 +25366,12 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -25385,13 +25385,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>48666.24</v>
+        <v>2521.57</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>799512-676-CM26</t>
+          <t>899-413-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25416,12 +25416,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>61.602.067-6</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25431,17 +25431,17 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -25450,13 +25450,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>8350.110000000001</v>
+        <v>24553.03</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>899-413-CM26</t>
+          <t>799512-676-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25481,12 +25481,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>61.602.067-6</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25496,17 +25496,17 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -25515,13 +25515,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>24553.03</v>
+        <v>8350.110000000001</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2428-698-CM26</t>
+          <t>2428-699-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25561,17 +25561,17 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -25580,13 +25580,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>7143.05</v>
+        <v>2468.04</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2428-699-CM26</t>
+          <t>2428-698-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25626,17 +25626,17 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>2468.04</v>
+        <v>7143.05</v>
       </c>
     </row>
     <row r="395">
@@ -25777,7 +25777,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>836-114-CM26</t>
+          <t>836-115-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25797,7 +25797,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -25817,32 +25817,28 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>5084.16</v>
+        <v>6172.53</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>836-115-CM26</t>
+          <t>640840-100-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -25867,12 +25863,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -25882,28 +25878,32 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K398" t="inlineStr"/>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>6172.53</v>
+        <v>666.4</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>640840-100-CM26</t>
+          <t>4301-451-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -25928,12 +25928,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -25943,17 +25943,17 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -25962,13 +25962,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>666.4</v>
+        <v>1628.16</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>4301-451-CM26</t>
+          <t>836-114-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25988,17 +25988,17 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26008,17 +26008,17 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -26027,7 +26027,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1628.16</v>
+        <v>5084.16</v>
       </c>
     </row>
     <row r="401">
@@ -26163,7 +26163,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2428-732-CM26</t>
+          <t>799512-711-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26188,12 +26188,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -26203,17 +26203,17 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -26222,13 +26222,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1527.96</v>
+        <v>8306.1</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>799512-711-CM26</t>
+          <t>2428-732-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26253,12 +26253,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26268,17 +26268,17 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -26287,7 +26287,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>8306.1</v>
+        <v>1527.96</v>
       </c>
     </row>
     <row r="405">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -26358,7 +26358,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2755-272-CM26</t>
+          <t>1422256-31-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26378,17 +26378,17 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>65.099.506-6</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>ASOCIACION PARQUE CULTURAL DE VALPARAISO</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26417,7 +26417,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>13413.6</v>
+        <v>3845.18</v>
       </c>
     </row>
     <row r="407">
@@ -26484,7 +26484,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1422256-31-CM26</t>
+          <t>2755-272-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26509,12 +26509,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>65.099.506-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>ASOCIACION PARQUE CULTURAL DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26543,7 +26543,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3845.18</v>
+        <v>13413.6</v>
       </c>
     </row>
     <row r="409">
@@ -26610,7 +26610,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>640840-104-CM26</t>
+          <t>4469-621-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26635,12 +26635,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26650,17 +26650,17 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -26669,13 +26669,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1234.02</v>
+        <v>3571.52</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>4469-621-CM26</t>
+          <t>4469-622-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26715,17 +26715,17 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -26734,13 +26734,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>3571.52</v>
+        <v>2785.91</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>4469-622-CM26</t>
+          <t>640840-104-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26765,12 +26765,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -26780,17 +26780,17 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2785.91</v>
+        <v>1234.02</v>
       </c>
     </row>
     <row r="413">
@@ -26870,7 +26870,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2628-183-CM26</t>
+          <t>2687-121-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -26895,12 +26895,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -26910,12 +26910,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -26929,13 +26929,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>4641</v>
+        <v>3996.32</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2920-149-CM26</t>
+          <t>2628-183-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -26960,12 +26960,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -26975,12 +26975,12 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -26994,13 +26994,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1021.94</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2687-121-CM26</t>
+          <t>2920-149-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27020,17 +27020,17 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27040,12 +27040,12 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -27059,13 +27059,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>3996.32</v>
+        <v>1021.94</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2628-182-CM26</t>
+          <t>1134432-504-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27085,17 +27085,17 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27105,12 +27105,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -27124,13 +27124,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>3480.75</v>
+        <v>811.9299999999999</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>1134432-504-CM26</t>
+          <t>2628-182-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27150,17 +27150,17 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -27189,7 +27189,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>811.9299999999999</v>
+        <v>3480.75</v>
       </c>
     </row>
     <row r="419">
@@ -27256,7 +27256,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2688-241-CM26</t>
+          <t>1216085-317-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27281,12 +27281,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>70.983.600-5</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>CORP MUNICIPAL PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27296,17 +27296,17 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2435.78</v>
+        <v>67805.37</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1216085-317-CM26</t>
+          <t>2688-241-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27341,17 +27341,17 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>70.983.600-5</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27361,17 +27361,17 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -27380,7 +27380,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>67805.37</v>
+        <v>2435.78</v>
       </c>
     </row>
     <row r="422">
@@ -27451,7 +27451,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>4469-687-CM26</t>
+          <t>836-125-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27471,17 +27471,17 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27491,28 +27491,32 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K423" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>3212.88</v>
+        <v>5669.99</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>4469-686-CM26</t>
+          <t>1480972-376-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27532,17 +27536,17 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -27552,17 +27556,17 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -27571,13 +27575,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>3388.31</v>
+        <v>25074.55</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1480972-376-CM26</t>
+          <t>4469-686-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -27602,12 +27606,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -27617,17 +27621,17 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -27636,13 +27640,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>25074.55</v>
+        <v>3388.31</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>836-125-CM26</t>
+          <t>4469-687-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -27667,12 +27671,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -27682,32 +27686,28 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K426" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>5669.99</v>
+        <v>3212.88</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>3047-376-CM26</t>
+          <t>3035-321-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -27732,12 +27732,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -27747,32 +27747,28 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K427" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>10245.94</v>
+        <v>2258.62</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>3035-321-CM26</t>
+          <t>3047-376-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -27792,17 +27788,17 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -27812,28 +27808,32 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>2258.62</v>
+        <v>10245.94</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>640840-125-CM26</t>
+          <t>2428-793-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -27853,17 +27853,17 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -27873,17 +27873,17 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -27892,13 +27892,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1281.42</v>
+        <v>1055.16</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1080157-118-CM26</t>
+          <t>640840-125-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -27923,12 +27923,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -27938,17 +27938,17 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -27957,13 +27957,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>16063.57</v>
+        <v>1281.42</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2428-793-CM26</t>
+          <t>1080157-118-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -27983,17 +27983,17 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -28003,17 +28003,17 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -28022,13 +28022,13 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1055.16</v>
+        <v>16063.57</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>3035-328-CM26</t>
+          <t>4283-168-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -28053,12 +28053,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.050.900-8</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE CATEMU</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -28068,12 +28068,12 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -28087,13 +28087,13 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>849.17</v>
+        <v>791</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>4283-168-CM26</t>
+          <t>3035-328-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -28118,12 +28118,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>69.050.900-8</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CATEMU</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -28133,12 +28133,12 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -28152,7 +28152,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>791</v>
+        <v>849.17</v>
       </c>
     </row>
     <row r="434">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -28483,7 +28483,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2427-699-CM26</t>
+          <t>1480972-428-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28503,17 +28503,17 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28523,17 +28523,17 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -28542,13 +28542,13 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>7908.57</v>
+        <v>1628.16</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1480972-428-CM26</t>
+          <t>2427-699-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -28568,17 +28568,17 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -28588,17 +28588,17 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -28607,7 +28607,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1628.16</v>
+        <v>7908.57</v>
       </c>
     </row>
     <row r="441">
@@ -28678,7 +28678,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1134432-573-CM26</t>
+          <t>2756-128-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -28703,12 +28703,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28718,28 +28718,32 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2011.08</v>
+        <v>36750.67</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2756-128-CM26</t>
+          <t>1134432-573-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -28764,12 +28768,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -28779,26 +28783,22 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K443" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>36750.67</v>
+        <v>2011.08</v>
       </c>
     </row>
     <row r="444">
@@ -29320,7 +29320,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>5839-38-CM26</t>
+          <t>3091-110-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29345,12 +29345,12 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -29360,17 +29360,17 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -29379,13 +29379,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>30421.76</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>3091-110-CM26</t>
+          <t>5839-38-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -29425,17 +29425,17 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -29444,13 +29444,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>6097</v>
+        <v>30421.76</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>3561-399-CM26</t>
+          <t>2688-278-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29465,22 +29465,22 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29509,13 +29509,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>3597.95</v>
+        <v>2019.87</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2688-278-CM26</t>
+          <t>2783-760-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29535,17 +29535,17 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -29555,32 +29555,28 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K455" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2019.87</v>
+        <v>2498.99</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2783-760-CM26</t>
+          <t>3561-407-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -29595,7 +29591,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -29605,12 +29601,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -29620,12 +29616,12 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K456" t="inlineStr"/>
@@ -29635,13 +29631,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>2498.99</v>
+        <v>1520.82</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>3561-407-CM26</t>
+          <t>2783-767-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -29656,7 +29652,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -29666,12 +29662,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -29681,22 +29677,26 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K457" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>1520.82</v>
+        <v>4535.19</v>
       </c>
     </row>
     <row r="458">
@@ -29722,7 +29722,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -29767,7 +29767,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2783-767-CM26</t>
+          <t>4803-215-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -29782,7 +29782,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -29792,12 +29792,12 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -29807,12 +29807,12 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
@@ -29826,13 +29826,13 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>4535.19</v>
+        <v>260.09</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>4803-215-CM26</t>
+          <t>1202333-131-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -29857,12 +29857,12 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.060.700-K</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -29872,12 +29872,12 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
@@ -29891,13 +29891,13 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>260.09</v>
+        <v>76065.10000000001</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>1202333-131-CM26</t>
+          <t>1202333-132-CM26</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -29937,17 +29937,17 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -29956,13 +29956,13 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>76065.10000000001</v>
+        <v>38261.15</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>1202333-132-CM26</t>
+          <t>799512-917-CM26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -29977,22 +29977,22 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>69.060.700-K</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -30002,17 +30002,17 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -30021,13 +30021,13 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>38261.15</v>
+        <v>6803.99</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>799512-917-CM26</t>
+          <t>640840-161-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -30037,27 +30037,27 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -30067,17 +30067,17 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
@@ -30086,13 +30086,13 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>6803.99</v>
+        <v>37984.44</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>640840-161-CM26</t>
+          <t>2688-296-CM26</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -30107,22 +30107,22 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -30132,26 +30132,22 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K464" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>37984.44</v>
+        <v>418.88</v>
       </c>
     </row>
     <row r="465">
@@ -30218,7 +30214,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2688-296-CM26</t>
+          <t>3092-104-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30233,7 +30229,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -30243,12 +30239,12 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -30258,22 +30254,26 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K466" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>418.88</v>
+        <v>11055.03</v>
       </c>
     </row>
     <row r="467">
@@ -30470,7 +30470,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>3092-104-CM26</t>
+          <t>2131-118-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30485,22 +30485,22 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>60.511.057-6</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PETORCA</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -30510,17 +30510,17 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -30529,13 +30529,13 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>11055.03</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>4373-59-CM26</t>
+          <t>1350138-42-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -30555,17 +30555,17 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>60.511.053-3</t>
+          <t>60.511.056-8</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ISLA DE PASCUA</t>
+          <t>GOBERNACION PROVINCIAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -30575,28 +30575,32 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K471" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>3148.74</v>
+        <v>2101.54</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2131-118-CM26</t>
+          <t>1528-198-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -30616,17 +30620,17 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>60.511.057-6</t>
+          <t>60.511.052-5</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PETORCA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE QUILLOTA</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -30636,12 +30640,12 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
@@ -30655,13 +30659,13 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>3152.31</v>
+        <v>3154.81</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1350138-42-CM26</t>
+          <t>4373-59-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -30681,17 +30685,17 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>60.511.056-8</t>
+          <t>60.511.053-3</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>GOBERNACION PROVINCIAL DE LOS ANDES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -30701,32 +30705,28 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K473" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>2101.54</v>
+        <v>3148.74</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1528-198-CM26</t>
+          <t>3134-194-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -30741,7 +30741,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -30751,12 +30751,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>60.511.052-5</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE QUILLOTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -30766,12 +30766,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
@@ -30785,13 +30785,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>3154.81</v>
+        <v>251982.5</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>3134-194-CM26</t>
+          <t>5514-66-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -30811,17 +30811,17 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -30831,32 +30831,28 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
-        </is>
-      </c>
-      <c r="K475" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.011.397-2</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>251982.5</v>
+        <v>75485.50999999999</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>5514-66-CM26</t>
+          <t>2221-63-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -30876,17 +30872,17 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>60.511.055-k</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE SAN FELIPE DE ACONCAGUA</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -30896,22 +30892,26 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
-        </is>
-      </c>
-      <c r="K476" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>75485.50999999999</v>
+        <v>2101.54</v>
       </c>
     </row>
     <row r="477">
@@ -30982,7 +30982,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2221-63-CM26</t>
+          <t>4766-3634-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -30997,7 +30997,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -31007,12 +31007,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>60.511.055-k</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE SAN FELIPE DE ACONCAGUA</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -31022,32 +31022,28 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K478" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>2101.54</v>
+        <v>1975.4</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>4766-3634-CM26</t>
+          <t>1725-882-CC26</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -31072,12 +31068,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -31087,28 +31083,32 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K479" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>1975.4</v>
+        <v>94549.84</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1725-882-CC26</t>
+          <t>3015-109-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -31133,12 +31133,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -31148,12 +31148,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
@@ -31167,13 +31167,13 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>94549.84</v>
+        <v>1804.49</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>3015-109-CM26</t>
+          <t>2626-456-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -31188,7 +31188,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -31198,12 +31198,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -31213,12 +31213,12 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
@@ -31232,13 +31232,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1804.49</v>
+        <v>2373.01</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2626-456-CM26</t>
+          <t>878-30-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -31253,7 +31253,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -31263,12 +31263,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>60.511.050-9</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE VALPARAÍSO</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -31278,12 +31278,12 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
@@ -31297,13 +31297,13 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2373.01</v>
+        <v>2101.54</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>878-30-CM26</t>
+          <t>2932-116-CM26</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -31318,7 +31318,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -31328,12 +31328,12 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>60.511.050-9</t>
+          <t>60.511.054-1</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE VALPARAÍSO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -31368,7 +31368,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2932-116-CM26</t>
+          <t>2783-866-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31383,22 +31383,22 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>60.511.054-1</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -31408,17 +31408,17 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -31427,13 +31427,13 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>2101.54</v>
+        <v>469.55</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2783-866-CM26</t>
+          <t>2756-212-CM26</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -31448,22 +31448,22 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -31473,32 +31473,28 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K485" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr"/>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>469.55</v>
+        <v>26271.87</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2756-212-CM26</t>
+          <t>2428-1064-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -31523,12 +31519,12 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -31538,12 +31534,12 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K486" t="inlineStr"/>
@@ -31553,13 +31549,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>26271.87</v>
+        <v>901.89</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2428-1064-CM26</t>
+          <t>1359575-208-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -31574,7 +31570,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -31584,12 +31580,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -31599,22 +31595,26 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K487" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>901.89</v>
+        <v>11144.11</v>
       </c>
     </row>
     <row r="488">
@@ -31681,7 +31681,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>1359575-208-CM26</t>
+          <t>859378-624-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -31691,12 +31691,12 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>oct-2026</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -31721,32 +31721,28 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K489" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>11144.11</v>
+        <v>1226.51</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>859378-624-CM26</t>
+          <t>640840-181-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -31761,22 +31757,22 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -31786,28 +31782,32 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K490" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1226.51</v>
+        <v>433.64</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>640840-181-CM26</t>
+          <t>1480972-683-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -31832,12 +31832,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -31866,13 +31866,13 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>433.64</v>
+        <v>24797.16</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>1480972-683-CM26</t>
+          <t>1439295-15-CM26</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -31897,12 +31897,12 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>65.190.295-9</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>ASOCIACION DE MUNICIPALIDADES TURISTICAS DE CHILE</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -31912,17 +31912,17 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>24797.16</v>
+        <v>318.13</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>1439295-15-CM26</t>
+          <t>3117-1378-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -31952,7 +31952,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>65.190.295-9</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES TURISTICAS DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -31977,12 +31977,12 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
@@ -31996,13 +31996,13 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>318.13</v>
+        <v>693.45</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>3117-1378-CM26</t>
+          <t>2598-232-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -32027,12 +32027,12 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -32042,32 +32042,28 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K494" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>693.45</v>
+        <v>14843.82</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2598-232-CM26</t>
+          <t>2598-237-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -32082,7 +32078,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -32122,13 +32118,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>14843.82</v>
+        <v>3620.46</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2598-237-CM26</t>
+          <t>859378-631-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32148,17 +32144,17 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -32168,12 +32164,12 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
+          <t>76.086.318-1</t>
         </is>
       </c>
       <c r="K496" t="inlineStr"/>
@@ -32183,13 +32179,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>3620.46</v>
+        <v>31951.5</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>859378-631-CM26</t>
+          <t>4469-955-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32204,22 +32200,22 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -32229,12 +32225,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>76.086.318-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K497" t="inlineStr"/>
@@ -32244,13 +32240,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>31951.5</v>
+        <v>228.48</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>4469-955-CM26</t>
+          <t>2737-711-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32275,12 +32271,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -32305,13 +32301,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>228.48</v>
+        <v>987.7</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2737-711-CM26</t>
+          <t>2687-154-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32326,22 +32322,22 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -32351,28 +32347,32 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K499" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>987.7</v>
+        <v>8321.379999999999</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2783-923-CM26</t>
+          <t>2428-1136-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32397,12 +32397,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -32412,32 +32412,28 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K500" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>4160.69</v>
+        <v>11792.42</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2687-154-CM26</t>
+          <t>2783-923-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32457,17 +32453,17 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -32496,13 +32492,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>8321.379999999999</v>
+        <v>4160.69</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2428-1136-CM26</t>
+          <t>640840-190-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -32517,7 +32513,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -32527,12 +32523,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -32542,28 +32538,32 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
-        </is>
-      </c>
-      <c r="K502" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>11792.42</v>
+        <v>10275.07</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>640840-190-CM26</t>
+          <t>1480972-761-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -32588,12 +32588,12 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -32603,17 +32603,17 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -32622,13 +32622,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>10275.07</v>
+        <v>10504.13</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1480972-761-CM26</t>
+          <t>3084-155-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -32643,7 +32643,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -32653,12 +32653,12 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>61.967.700-5</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -32668,17 +32668,17 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -32687,13 +32687,13 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>10504.13</v>
+        <v>102525.64</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>3084-155-CM26</t>
+          <t>2026-1322-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -32718,12 +32718,12 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>61.967.700-5</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -32733,32 +32733,28 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
-        </is>
-      </c>
-      <c r="K505" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>102525.64</v>
+        <v>13072</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2026-1322-CM26</t>
+          <t>3047-609-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -32773,7 +32769,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -32783,12 +32779,12 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -32798,28 +32794,32 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K506" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>13072</v>
+        <v>2912.98</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>3047-609-CM26</t>
+          <t>2832-921-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -32834,7 +32834,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -32844,12 +32844,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -32859,12 +32859,12 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
@@ -32878,13 +32878,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2912.98</v>
+        <v>15463.81</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2832-921-CM26</t>
+          <t>1305525-218-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -32909,12 +32909,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>61.981.120-8</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -32924,12 +32924,12 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
@@ -32943,13 +32943,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>15463.81</v>
+        <v>5354.88</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>1305525-218-CM26</t>
+          <t>1305525-219-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -32989,12 +32989,12 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
@@ -33008,13 +33008,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>5354.88</v>
+        <v>42102.2</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>1305525-219-CM26</t>
+          <t>1725-1074-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33039,12 +33039,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>61.981.120-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -33054,12 +33054,12 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
@@ -33073,13 +33073,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>42102.2</v>
+        <v>23473.64</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1725-1074-CM26</t>
+          <t>5514-86-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33094,7 +33094,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -33104,12 +33104,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -33119,86 +33119,21 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K511" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.011.397-2</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>23473.64</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>5514-86-CM26</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="E512" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F512" t="inlineStr">
-        <is>
-          <t>60.201.000-7</t>
-        </is>
-      </c>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>SENADO DE LA REPUBLICA</t>
-        </is>
-      </c>
-      <c r="H512" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I512" t="inlineStr">
-        <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
-        </is>
-      </c>
-      <c r="J512" t="inlineStr">
-        <is>
-          <t>76.011.397-2</t>
-        </is>
-      </c>
-      <c r="K512" t="inlineStr"/>
-      <c r="L512" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M512" s="2" t="n">
         <v>37742.75</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/valparaiso.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/valparaiso.xlsx
@@ -32392,7 +32392,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
